--- a/05_Current_Prototype/data/examples/site/electrical-sample.xlsx
+++ b/05_Current_Prototype/data/examples/site/electrical-sample.xlsx
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>91.59999999999999</v>
+        <v>25.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.99</v>
+        <v>9.26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45881.42</v>
+        <v>45875.49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83.5</v>
+        <v>23.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.08</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>45888.94</v>
+        <v>45877.61</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>88.7</v>
+        <v>24.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>31.87</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>45896.91</v>
+        <v>45879.84</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1786,7 +1786,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>92.40000000000001</v>
+        <v>26</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>33.69</v>
+        <v>9.48</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>45905.33</v>
+        <v>45882.21</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2246,7 +2246,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>87.7</v>
+        <v>24.7</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31.56</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>45913.22</v>
+        <v>45884.44</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>85.09999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.23</v>
+        <v>8.49</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>45920.78</v>
+        <v>45886.56</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>88.2</v>
+        <v>24.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>32.47</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>45928.9</v>
+        <v>45888.84</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3211,7 +3211,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>87.3</v>
+        <v>24.6</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31.53</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>45936.78</v>
+        <v>45891.06</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>85.7</v>
+        <v>24.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.57</v>
+        <v>8.6</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>45944.42</v>
+        <v>45893.21</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EMS-FDMCHL01</t>
+          <t>EMS-FDMAHU01</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
